--- a/sources/ganryu_step8c.xlsx
+++ b/sources/ganryu_step8c.xlsx
@@ -857,6 +857,11 @@
           <t>Opponent can tech roll after the throw.</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
@@ -924,6 +929,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
@@ -991,6 +1001,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
@@ -1048,6 +1063,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
@@ -1108,6 +1128,11 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>06da1e67-d557-429d-bbe8-0414aa87e38a</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">

--- a/sources/ganryu_step8c.xlsx
+++ b/sources/ganryu_step8c.xlsx
@@ -417,38 +417,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AD100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="54" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col hidden="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col hidden="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col hidden="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col hidden="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col hidden="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col hidden="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="98" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="38" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col hidden="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col hidden="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col hidden="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col hidden="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col hidden="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col hidden="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="98" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="38" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,125 +482,130 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -616,57 +622,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Body Drop</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Body Drop</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>752aa677-a50d-4833-bb06-d67f5506b282</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>6c49d9b3-f9d5-4774-8ac3-1a827964aac2</t>
         </is>
@@ -683,57 +689,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Hip Toss</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Hip Toss</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2b5a6100-8a10-414e-8ec5-2d815867382f</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>4b47b69f-f1bc-4229-b54e-47908c647035</t>
         </is>
@@ -750,57 +756,57 @@
           <t>f,f+2+3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Jizo Hug</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Jizo Hug</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>07c657e8-e757-4555-90a6-f7255dba001a</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>87b88dcb-4148-4126-ad19-3e929519dcfa</t>
         </is>
@@ -817,57 +823,57 @@
           <t>f+2+4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Lifting Toss</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Lifting Toss</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Opponent can tech roll after the throw.</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -891,55 +897,60 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Upper Stream</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Upper Stream</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -963,55 +974,60 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Crotch Slam</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Crotch Slam</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1028,52 +1044,52 @@
           <t>d+1+2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Pedal Press</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Pedal Press</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1097,50 +1113,55 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Reverse Choke Slam</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Reverse Choke Slam</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>06da1e67-d557-429d-bbe8-0414aa87e38a</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>06da1e67-d557-429d-bbe8-0414aa87e38a</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1177,125 +1198,130 @@
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="M13" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="P13" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
+      <c r="Q13" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q13" s="1" t="inlineStr">
+      <c r="R13" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R13" s="1" t="inlineStr">
+      <c r="S13" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S13" s="1" t="inlineStr">
+      <c r="T13" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T13" s="1" t="inlineStr">
+      <c r="U13" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U13" s="1" t="inlineStr">
+      <c r="V13" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V13" s="1" t="inlineStr">
+      <c r="W13" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W13" s="1" t="inlineStr">
+      <c r="X13" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X13" s="1" t="inlineStr">
+      <c r="Y13" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="AA13" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
+      <c r="AB13" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB13" s="1" t="inlineStr">
+      <c r="AC13" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC13" s="1" t="inlineStr">
+      <c r="AD13" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1312,77 +1338,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>1bf81c40-273e-419e-8218-6cb5c1ba268b</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>fa15e532-cc7e-449e-b2a4-4531979ae5db</t>
         </is>
@@ -1399,77 +1425,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>663344c0-15d7-47c2-b97c-66d4e81f2e64</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>bd55a571-ccc3-4ecb-87e5-79cb6850d9b6</t>
         </is>
@@ -1486,77 +1512,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>bde4e038-4736-4e02-ae0d-9b710af8d9b9</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>482bb902-f2b2-4eae-8bdf-c1d349b38b06</t>
         </is>
@@ -1573,77 +1599,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>d02c08f2-461c-45e5-abde-d4aeeda5fa0f</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>fdf12daa-d5b1-489a-b560-40e811661913</t>
         </is>
@@ -1660,77 +1686,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>1e8cf19a-368b-427b-9d5f-4b9a7e7b28f7</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>c59afd9b-68a3-421f-aa77-5a940a987426</t>
         </is>
@@ -1747,77 +1773,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>d8112dcc-436f-483e-ad38-81a6a38b0fd9</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>c8509491-a7a9-4e46-91b8-ab526539fe3c</t>
         </is>
@@ -1834,77 +1860,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>20f6e116-b693-4dd5-80fb-ff7217047dfe</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>79c4977f-4e21-4e16-9826-209c7670a29b</t>
         </is>
@@ -1921,77 +1947,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>85450c59-e23e-4fec-bc33-ee33580952a7</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>342b7f84-21b5-4589-a5b4-b0ba1be2203e</t>
         </is>
@@ -2008,77 +2034,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>b79c987b-7ac5-49a1-b9b2-76f4daf3a511</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>e437b4ec-a97e-4267-ae33-8bf53c2897b8</t>
         </is>
@@ -2095,77 +2121,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-24</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-24</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>41b81282-24c8-478d-9d3e-5c37c76aaf80</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>d89034c0-4140-4ef6-ab97-2b5060df4e2c</t>
         </is>
@@ -2182,77 +2208,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>95ee3bae-1d43-4b20-8aa4-92c01c218b95</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>0a3960d9-7519-486e-8494-2e85f84d25ac</t>
         </is>
@@ -2269,77 +2295,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-24</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-24</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>33483703-9385-4745-90c2-5f09b7c0af3f</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>93e1f128-4672-4123-9f29-9269136bc8df</t>
         </is>
@@ -2356,77 +2382,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>327e4093-3d77-4d7b-a0b5-6a8b7f20ce5b</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>0d4044ae-614e-44e4-9938-624f4e1367d7</t>
         </is>
@@ -2443,77 +2469,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>b0b3a0dc-69e3-4048-8764-5061e4e95db8</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>9b58bea7-89e4-43de-8366-dce70b3f0d22</t>
         </is>
@@ -2530,77 +2556,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2cda2606-1a34-4f36-b785-886c3018d2d4</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>219405f1-2fb7-4f27-9972-c1fe555145da</t>
         </is>
@@ -2617,77 +2643,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>aacf5a62-ce99-4f9a-975e-202e1f38f79a</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>86a0053b-bcd9-4348-8fe4-7f837c5bd0c7</t>
         </is>
@@ -2704,77 +2730,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>7820ff42-69b8-4ef5-987e-e8b2dfa69a5f</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>effd71a3-e332-4a72-9dfe-053a2956c609</t>
         </is>
@@ -2791,77 +2817,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>dfc01afe-8990-498a-a110-a3643cd4ce51</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>4d53468b-e0b1-4a60-8e8a-9c1937461f0a</t>
         </is>
@@ -2878,77 +2904,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>e46a986b-3c19-4ff1-ab47-2d7780b2a9c1</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>02d192b4-fd41-4133-9803-5d1998a3d6f0</t>
         </is>
@@ -2965,77 +2991,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>041e5ee1-602b-4f6d-ad16-e95314d6cab3</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>55a39460-a7fa-4c9f-9a8a-b52fe4471509</t>
         </is>
@@ -3052,77 +3078,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>03cd905d-6db9-4486-a38e-9e6859609498</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>3567ba09-a7f8-4e2c-899e-cc72332e8cc0</t>
         </is>
@@ -3139,77 +3165,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>9139021d-4403-46c1-87fa-00a34b90b6ee</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>5f9c1213-0e4c-435c-bddd-a2f1f00729e4</t>
         </is>
@@ -3226,77 +3252,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>466b0cf4-6898-4468-8aa1-4b56be85ed86</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>6ca50bba-a859-4f42-8e5d-d4368b7381b2</t>
         </is>
@@ -3313,77 +3339,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>aaaa0140-eab1-4e55-aad0-2a7bc6aa4ace</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>0807bbb3-5a72-4d23-81b3-0dfd9f1f93ff</t>
         </is>
@@ -3420,125 +3446,130 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="I40" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="K40" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K40" s="1" t="inlineStr">
+      <c r="L40" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L40" s="1" t="inlineStr">
+      <c r="M40" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M40" s="1" t="inlineStr">
+      <c r="N40" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N40" s="1" t="inlineStr">
+      <c r="O40" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O40" s="1" t="inlineStr">
+      <c r="P40" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="Q40" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
+      <c r="R40" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R40" s="1" t="inlineStr">
+      <c r="S40" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S40" s="1" t="inlineStr">
+      <c r="T40" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T40" s="1" t="inlineStr">
+      <c r="U40" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U40" s="1" t="inlineStr">
+      <c r="V40" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V40" s="1" t="inlineStr">
+      <c r="W40" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W40" s="1" t="inlineStr">
+      <c r="X40" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X40" s="1" t="inlineStr">
+      <c r="Y40" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr">
+      <c r="Z40" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z40" s="1" t="inlineStr">
+      <c r="AA40" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA40" s="1" t="inlineStr">
+      <c r="AB40" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB40" s="1" t="inlineStr">
+      <c r="AC40" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC40" s="1" t="inlineStr">
+      <c r="AD40" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3555,87 +3586,87 @@
           <t>SS+1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Falling Hammer</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Falling Hammer</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>92714721-8006-4ba1-8584-5f3d6de25d9b</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>9ba966c8-0e28-49f6-8fb3-8ff645caaa69</t>
         </is>
@@ -3652,87 +3683,87 @@
           <t>1 ,1 ,1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Sumo Hammer</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Sumo Hammer</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-7 -9 -13</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-7 -9 -13</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>+4 +2 KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>+4 +2 KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>18,15,18</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>18,15,18</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>e3a95492-8eeb-45b7-a089-34e76ce26845</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>eb905c9c-fef7-4e0d-9c39-ee4a54793d65</t>
         </is>
@@ -3741,100 +3772,100 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,1</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+          <t>DF,1 ,2 ,1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Left Nodowa Rush</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Left Nodowa Rush</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-10 -9 -8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>-10 -9 -8</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>+1 +2 +2</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>+1 +2 +2</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>+1 +2 +2</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>+1 +2 +2</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>9,12,12</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>9,12,12</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>dd5b1029-a152-44e0-8179-0527f3405e4c</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>7506cfeb-5e88-4fd6-afad-0511be4d6e5e</t>
         </is>
@@ -3843,100 +3874,100 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Df+2 ,1 ,2</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+          <t>DF,2 ,1 ,2</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Right Nodowa Rush</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Right Nodowa Rush</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-9 -8 -9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-9 -8 -9</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+2 +2 +3</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+2 +2 +3</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+2 +2 +3</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>+2 +2 +3</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>15,12,12</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>15,12,12</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>31d5c8ab-c220-4dd2-b25f-d4df0ea6ff82</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>cc891c3f-872f-4b9f-ad52-dc926cb673bf</t>
         </is>
@@ -3953,87 +3984,87 @@
           <t>FC+df+1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Windmill Rush</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Windmill Rush</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-9 -8 -9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-9 -8 -9</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>+2 +3 +3</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>+2 +3 +3</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>+2 +3 +3</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>+2 +3 +3</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>12,15,15</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>12,15,15</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>f4b84634-a7aa-4896-9939-368c0bd3b572</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>ecfa6d11-fd22-4f40-81de-25da975b166e</t>
         </is>
@@ -4050,92 +4081,92 @@
           <t>FC+df+1 ,2 ,1 ,1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>– Windmill Backhand</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Windmill Rush – Windmill Backhand</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-9 -8 -9 -14</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>+2 +3 +3 KD</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>+2 +3 +3 KD</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>12,15,15,30</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>mmmh</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>CF GB</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>0e919272-147b-42cc-9b17-12f23ce932bc</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>50e273a7-d2bd-4bed-bfaa-5ab1031bfd45</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>f4b84634-a7aa-4896-9939-368c0bd3b572</t>
         </is>
@@ -4152,92 +4183,92 @@
           <t>FC+1 ,1 ,1 ,2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Hammer Rush</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Hammer Rush</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-8 +1 -12 -9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-8 +1 -12 -9</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>+2 +12 -1 +2</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+2 +12 -1 +2</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>KD +12 -1 +2</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>KD +12 -1 +2</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>10,8,12,12</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>10,8,12,12</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>18deffcb-bbb7-40c1-af66-81b63faa850e</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>013d4ccd-433f-402c-88a2-e3290326fe80</t>
         </is>
@@ -4254,87 +4285,87 @@
           <t>FC+1 ,1 ,1 ,2 ,f+1</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-8 +1 -12 -9 -17</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+2 +12 -1 +2 -6</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>KD +12 -1 +2 -6</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>10,8,12,12,12</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>LLmmh</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>e362987d-59e2-460f-8fcd-62927d0119c1</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>edfa4f95-b017-46e2-a42d-69d63d6cc585</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>18deffcb-bbb7-40c1-af66-81b63faa850e</t>
         </is>
@@ -4351,92 +4382,92 @@
           <t>FC+1 ,1 ,1 ,2 ,df+1</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-8 +1 -12 -9 -1</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+2 +12 -1 +2 +10</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>KD +12 -1 +2 +10</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>10,8,12,12,15</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>LLmmm</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>468a8105-64cb-4f62-98bb-7e68b00b6011</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>0fbc1466-bc2f-4d31-bd62-21c19707e9a5</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>18deffcb-bbb7-40c1-af66-81b63faa850e</t>
         </is>
@@ -4453,92 +4484,92 @@
           <t>FC+1 ,1 ,1 ,2 ,d+1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-8 +1 -12 -9 -17</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>+2 +12 -1 +2 -7</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>KD +12 -1 +2 -7</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>10,8,12,12,8</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>LLmmL</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>7ea4c118-b2e1-40dc-a947-513690d9ce5a</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>e8b83ffd-6a75-416a-80bc-da796fbc1f26</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>18deffcb-bbb7-40c1-af66-81b63faa850e</t>
         </is>
@@ -4555,87 +4586,87 @@
           <t>f+1 ,2 ,1 ,2 ,1 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Devil Palm Thrusts</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Devil Palm Thrusts</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>(5x +1) -7 -11 -7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>(5x +1) -7 -11 -7</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>(5x +12) +4 0 +4</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>(5x +12) +4 0 +4</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>(5x +12) +4 0 +4</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>(5x +12) +4 0 +4</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>12,10,8,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>12,10,8,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>hhhhhhhh</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>hhhhhhhh</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>57f674d4-1f21-425c-9aa8-51419ef5d08e</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>5cf39cff-07e5-47da-bb5e-be4fa973a037</t>
         </is>
@@ -4652,97 +4683,97 @@
           <t>b,db,d,DF+1</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Sumo Mega Upper</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Sumo Mega Upper</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>70d535b5-f72a-4feb-96e8-e3ba9c94c2c3</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>55f4e3e3-caea-455b-824e-bed22d944429</t>
         </is>
@@ -4759,87 +4790,87 @@
           <t>1+2 &lt;1+2</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Hammer Chop - Hammer Upper</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Hammer Chop - Hammer Upper</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-15 -22</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-15 -22</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>21,22</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>21,22</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>cb3ee0ed-db63-47e3-be12-aaec16608990</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>f516dfc6-6f83-4075-a7d8-7bfbe6c49969</t>
         </is>
@@ -4856,92 +4887,92 @@
           <t>WS+1+2 &lt;1+2</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Hammer Upper - Hammer Chop</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Hammer Upper - Hammer Chop</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-16 -1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-16 -1</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>-5 +23</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>-5 +23</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>-5 KD</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>21,17</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>21,17</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>KS GB</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>e0d8bc5c-6cea-43ad-959d-a82d3e9c5215</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>93628611-e93f-49d9-b171-5a3559a12e30</t>
         </is>
@@ -4958,92 +4989,92 @@
           <t>FC+1+2</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Palm Lift</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Palm Lift</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>1788fefe-ac17-46a7-97e8-2fc4dd60a546</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>74af009f-23a1-4b07-885b-14a897332adb</t>
         </is>
@@ -5067,90 +5098,95 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>d+1+2</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>Pedal Press</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Pedal Press</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>SH GB</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>35b589e4-da87-46cc-823f-783083d6aa5d</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>6a93a783-c1df-452c-8432-23215361be78</t>
         </is>
@@ -5167,92 +5203,92 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Sumo Charge</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Sumo Charge</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>9d35bc4f-ccc2-4e67-ab1f-2a2c51fb5a48</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>6686cc22-3c87-4331-a5ca-b9e7829b071b</t>
         </is>
@@ -5276,90 +5312,95 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>F+1+2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>Sumo Scissors</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Sumo Scissors</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>b48ea104-eed9-4d6f-b23e-497b011ab156</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>6974bbb5-ce62-4393-b4e2-db39a1204efd</t>
         </is>
@@ -5376,92 +5417,92 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Palm Upper</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Palm Upper</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>aad795cd-c7f5-41b6-ae99-321fb5b2f9f5</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>28aa70f2-2d8f-49ae-b2be-9f195172b212</t>
         </is>
@@ -5478,87 +5519,87 @@
           <t>df+2 ,1 ,2 ,1 ,2 ,1 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>– Devil Palm Thrusts</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Palm Upper – Devil Palm Thrusts</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>(5x +1) -7 -11 -7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-5 (5x +1) -7 -11 -7</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>(5x +12) +4 0 +4</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>KD (5x +12) +4 0 +4</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>(5x +12) +4 0 +4</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>KD (5x +12) +4 0 +4</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>10,10,8,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>15,10,10,8,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>hhhhhhhh</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>mhhhhhhhh</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>a509e412-05c3-4073-8dda-b338929cfae0</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>de78aecf-6352-40ab-9525-8d71522e8d6c</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>aad795cd-c7f5-41b6-ae99-321fb5b2f9f5</t>
         </is>
@@ -5582,85 +5623,90 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>F+2,1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Jab - Elbow</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Jab - Elbow</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>0 +1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>0 +1</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>+11 +2</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>+11 +2</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>14,12</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>14,12</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>a06bb023-d9d3-47d5-86d5-d544fab56a18</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>0acb5e4b-e19a-4322-af34-cb2430a6d0d9</t>
         </is>
@@ -5677,92 +5723,92 @@
           <t>b,db,d,DF+2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Megaton Palm</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Megaton Palm</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>b988364f-377f-47e5-9809-745a0ad84e64</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>54ba695a-7bd7-41ae-8fdb-a664d763046f</t>
         </is>
@@ -5779,92 +5825,92 @@
           <t>d+2 ,2 ,2 ,2 ,2...</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Kabuki Dance</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Kabuki Dance</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-24 -24 -24 -24...</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-24 -24 -24 -24...</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>-6 -6 -6 -6 -6...</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>-6 -6 -6 -6 -6...</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>-6 -6 -6 -6 -6...</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>-6 -6 -6 -6 -6...</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>15,15,10,10,10...</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>15,15,10,10,10...</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>15,15,10,10,10...</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>sllll...</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>sllll...</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Can be continued indefinately.</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>6782ec01-e3c9-47aa-b585-ea7ecd67cc34</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>525507b4-1db5-4596-80b7-692598f0baef</t>
         </is>
@@ -5881,92 +5927,92 @@
           <t>df+2+3</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Thunder Slap</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Thunder Slap</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>JG RC</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>36cb20d4-91a8-41d2-8d23-cd89b2f47bff</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>0584250c-b736-4031-97a4-f25f80d9d17c</t>
         </is>
@@ -5983,97 +6029,97 @@
           <t>b+2</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Salt Shaker</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Salt Shaker</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>JG GB</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>8abdda1f-127d-4868-8180-b8bd267a1c19</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>b17d62a0-b0eb-4b68-b048-2d845d51b459</t>
         </is>
@@ -6090,87 +6136,87 @@
           <t>2 ,1 ,2 ,1 ,2 ,1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Devil Palm Thrusts</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Devil Palm Thrusts</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>(4x +1) -7 -11 -7 -11</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>(4x +1) -7 -11 -7 -11</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>(4x +7) +4 0 +4 0</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>(4x +7) +4 0 +4 0</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>(4x +7) +4 0 +4 0</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>(4x +7) +4 0 +4 0</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>12,10,8,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>12,10,8,5,5,5,5,5</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>hhhhhhhh</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>hhhhhhhh</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>c7add1a6-8de5-4bb3-9cbe-02be6a4706d9</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>557bb01a-64c2-4070-afea-76170f4d2e04</t>
         </is>
@@ -6187,92 +6233,92 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Sand Sweeper</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Sand Sweeper</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>d3f1a903-1a20-454b-a49f-365cc4c388d3</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>4e6f7cf6-030c-4d61-bc77-2115a1beb483</t>
         </is>
@@ -6289,87 +6335,87 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Thigh Quake</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Thigh Quake</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-24</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-24</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>7ac6ea0f-c3c1-41d3-99b3-8a3db04d85ba</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>d70637f2-b3da-4ed1-a2ca-a04acce3b8bd</t>
         </is>
@@ -6386,52 +6432,52 @@
           <t>WR+3+4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Sumo Slide</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Sumo Slide</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>(m_L)</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>(m_L)</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Hits mid at the start of the move or low at the end. It only hits once. Damage remains the same.</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>72a7c8c3-112b-4d7d-9e8a-bf21a29c6530</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>3d69a2b6-7320-4917-90e8-d84987ae3887</t>
         </is>
@@ -6455,45 +6501,50 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>d+3+4</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Sumo Sit</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Sumo Sit</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>63fd6dbd-e766-4231-90d3-9f85a615b035</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>e01e7ebe-c227-4727-bcf4-a8b8b5cf1b97</t>
         </is>
@@ -6510,87 +6561,87 @@
           <t>3+4 ,1</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>– Sit Thrust</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Sumo Sit – Sit Thrust</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>-,27</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>162e834d-aaec-4659-b498-f360223026ba</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>82564170-c0bd-4ad1-bedc-189979acab02</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>63fd6dbd-e766-4231-90d3-9f85a615b035</t>
         </is>
@@ -6607,92 +6658,92 @@
           <t>3+4 ,2</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>– Sit Sweep</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Sumo Sit – Sit Sweep</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>-,12</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>-L</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>JG RC</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>aed9fef5-5408-411e-ba41-963379429fb1</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>96f4b0f2-5f7f-4711-b2d7-6cb656d4d2ea</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>63fd6dbd-e766-4231-90d3-9f85a615b035</t>
         </is>
@@ -6709,52 +6760,52 @@
           <t>3+4,F</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>– Roll Forward</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Sumo Sit – Roll Forward</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>606e8c72-6180-4bfc-9ede-51eb6e1f8ea4</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>44f0fecb-6fd2-42de-8008-d28500d95121</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
+      <c r="AC73" t="inlineStr">
         <is>
           <t>63fd6dbd-e766-4231-90d3-9f85a615b035</t>
         </is>
@@ -6771,52 +6822,52 @@
           <t>3+4,B</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Sumo Sit – Roll Back</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>634fab0f-6214-4bc2-8929-4e74f0c55f0e</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>63a39785-f8c2-4bb7-8481-f87d0d48bc00</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
+      <c r="AC74" t="inlineStr">
         <is>
           <t>63fd6dbd-e766-4231-90d3-9f85a615b035</t>
         </is>
@@ -6833,52 +6884,52 @@
           <t>3+4~D</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>– Splits</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Sumo Sit – Splits</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>7769e34c-afc9-4345-a729-3bbc1035025e</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>2188d4d6-18f3-4a1b-962d-7f2e8cb48911</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>63fd6dbd-e766-4231-90d3-9f85a615b035</t>
         </is>
@@ -6895,52 +6946,62 @@
           <t>3+4~D,u</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>3+4~D,d</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>–– Splits Side Step</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Sumo Sit – Splits – Splits Side Step</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>-,-,-</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>91ee31e2-77e6-4c0a-95ce-fc89e97869e3</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>ec38c279-aa7a-47ea-8645-8585e33806cf</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>7769e34c-afc9-4345-a729-3bbc1035025e</t>
         </is>
@@ -6957,87 +7018,87 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Sumo Squash - Sumo Sit</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Sumo Squash - Sumo Sit</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>bb8b2c3f-0b6f-4280-84b0-6f088b0aeb2c</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>3f0982cf-862c-48ec-9ae6-1a2d8c4f37b1</t>
         </is>
@@ -7054,92 +7115,92 @@
           <t>uf+3+4 ,1</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>– Sit Thrust</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Sumo Squash - Sumo Sit – Sit Thrust</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>-1 +3</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>+10 +3</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>+10 +3</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>26,27</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>Mm</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>e98b12b8-d27d-43a8-bd9e-5849a8842f0f</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>ecb34ecb-002b-4b17-9153-940e80485fcd</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>bb8b2c3f-0b6f-4280-84b0-6f088b0aeb2c</t>
         </is>
@@ -7156,97 +7217,97 @@
           <t>uf+3+4 ,2</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>– Sit Sweep</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Sumo Squash - Sumo Sit – Sit Sweep</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-1 -20</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>+10 KD</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>+10 KD</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>26,12</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>JG RC</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>cf0cf6be-1dc1-4879-92c0-9f48445f8680</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>a517e615-f9d1-417b-8017-ab427d508e79</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AC79" t="inlineStr">
         <is>
           <t>bb8b2c3f-0b6f-4280-84b0-6f088b0aeb2c</t>
         </is>
@@ -7263,77 +7324,77 @@
           <t>uf+3+4,F</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>– Roll Forward</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Sumo Squash - Sumo Sit – Roll Forward</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>26,-</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>M-</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>You will roll back if the Sumo Squash connected.</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>91dfeae5-a3eb-4c59-b1d6-ee82a38b4e0e</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>36642f7f-ede9-4c83-b263-9e90cb01439c</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
+      <c r="AC80" t="inlineStr">
         <is>
           <t>bb8b2c3f-0b6f-4280-84b0-6f088b0aeb2c</t>
         </is>
@@ -7350,77 +7411,77 @@
           <t>uf+3+4,B</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Sumo Squash - Sumo Sit – Roll Back</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>26,-</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>M-</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>You will roll back if the Sumo Squash connected.</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>9d22baaa-6765-47c5-b7d0-b44ece721f71</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>dcbe1311-34a4-4444-bcc9-bc67318203bc</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>bb8b2c3f-0b6f-4280-84b0-6f088b0aeb2c</t>
         </is>
@@ -7437,72 +7498,72 @@
           <t>uf+3+4~D</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>– Splits</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Sumo Squash - Sumo Sit – Splits</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>26,-</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>M-</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>0fb45f9e-efba-4edf-a86f-37ed43d7390c</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>9254c5c7-0157-441e-b1d2-7a5dad19831f</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AC82" t="inlineStr">
         <is>
           <t>bb8b2c3f-0b6f-4280-84b0-6f088b0aeb2c</t>
         </is>
@@ -7519,175 +7580,195 @@
           <t>uf+3+4~D,u</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>uf+3+4~D,d</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>–– Splits Side Step</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Sumo Squash - Sumo Sit – Splits – Splits Side Step</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>26,-,-</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>M--</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>cd9f0bca-8832-4128-ab9b-83d621be1132</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>4c8f966a-2f38-4b5f-bb8f-2b2d72dc836a</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
+      <c r="AC83" t="inlineStr">
         <is>
           <t>0fb45f9e-efba-4edf-a86f-37ed43d7390c</t>
         </is>
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
+          <t>d+1+2</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Spring Hammer - Sumo Sit</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Spring Hammer - Sumo Sit</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>2d9ea837-881c-41c2-a708-b11ed56e45ed</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>a5255860-7291-46aa-bb42-4a90f233af01</t>
         </is>
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>– 2</t>
@@ -7695,106 +7776,111 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KND d+1+2 ,2</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
+          <t>d+1+2 ,2</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>– Sit Sweep</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Spring Hammer - Sumo Sit – Sit Sweep</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>+8 -20</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>+24 KD</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>+24 KD</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>12,12</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>JG RC</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>74800087-4e78-419d-a8d0-c4361038c1ba</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>d81f451b-737b-46d6-a072-681d8b707c35</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
+      <c r="AC85" t="inlineStr">
         <is>
           <t>2d9ea837-881c-41c2-a708-b11ed56e45ed</t>
         </is>
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>– F</t>
@@ -7802,81 +7888,86 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KND d+1+2,F</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
+          <t>d+1+2,F</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>– Roll Forward</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Spring Hammer - Sumo Sit – Roll Forward</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>12,-</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>m-</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>2b41d150-ebef-4b5e-b36e-a07918ce25c6</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>2f4377b0-3ed4-4a0b-8016-60af8b9d6261</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
+      <c r="AC86" t="inlineStr">
         <is>
           <t>2d9ea837-881c-41c2-a708-b11ed56e45ed</t>
         </is>
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>– B</t>
@@ -7884,81 +7975,86 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KND d+1+2,B</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
+          <t>d+1+2,B</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Spring Hammer - Sumo Sit – Roll Back</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>12,-</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>m-</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>9e1331a8-4561-4283-9e8f-9bc7326911fa</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>921b4197-4f0b-47aa-a42f-59c49d878d6e</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
+      <c r="AC87" t="inlineStr">
         <is>
           <t>2d9ea837-881c-41c2-a708-b11ed56e45ed</t>
         </is>
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>– ~D</t>
@@ -7966,81 +8062,86 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KND d+1+2~D</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
+          <t>d+1+2~D</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>– Splits</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Spring Hammer - Sumo Sit – Splits</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>12,-</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>m-</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>b4b24070-39b7-4f4b-bc4e-200edc67eebe</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>6e9d0ed2-9e0f-437d-9cd6-4955ce85e431</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
+      <c r="AC88" t="inlineStr">
         <is>
           <t>2d9ea837-881c-41c2-a708-b11ed56e45ed</t>
         </is>
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>–– u</t>
@@ -8048,75 +8149,85 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KND d+1+2~D,u</t>
+          <t>d+1+2~D,u</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>d</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>KND d+1+2~D,d</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>–– Splits Side Step</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Spring Hammer - Sumo Sit – Splits – Splits Side Step</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>12,-,-</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>m--</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>5f162acc-5bae-453b-bdb7-f6faa71061b7</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>fe689073-81dc-4af4-8b37-a3fc490734a3</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
+      <c r="AC89" t="inlineStr">
         <is>
           <t>b4b24070-39b7-4f4b-bc4e-200edc67eebe</t>
         </is>
@@ -8140,45 +8251,50 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>b+2+4</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>High &amp; Mid Punch Parry</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>High &amp; Mid Punch Parry</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>35695314-8ed6-4266-b6ff-84b2c6ceecb0</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>c65f4d9b-12e2-4205-ae43-d408cd84cf3d</t>
         </is>
@@ -8195,62 +8311,62 @@
           <t>b+1+3 ~1+2</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>– Pedal Press</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>High &amp; Mid Punch Parry – Pedal Press</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>-,22</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>throw</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>-throw</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>6a8ec6c5-a25d-4093-a2ed-7f9329ee3b86</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>b8eaa44f-8a90-4ac7-b86b-efb20029dd3d</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
+      <c r="AC91" t="inlineStr">
         <is>
           <t>35695314-8ed6-4266-b6ff-84b2c6ceecb0</t>
         </is>
@@ -8287,125 +8403,130 @@
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F94" s="1" t="inlineStr">
+      <c r="G94" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr">
+      <c r="H94" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H94" s="1" t="inlineStr">
+      <c r="I94" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I94" s="1" t="inlineStr">
+      <c r="J94" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J94" s="1" t="inlineStr">
+      <c r="K94" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K94" s="1" t="inlineStr">
+      <c r="L94" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L94" s="1" t="inlineStr">
+      <c r="M94" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M94" s="1" t="inlineStr">
+      <c r="N94" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N94" s="1" t="inlineStr">
+      <c r="O94" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O94" s="1" t="inlineStr">
+      <c r="P94" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P94" s="1" t="inlineStr">
+      <c r="Q94" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q94" s="1" t="inlineStr">
+      <c r="R94" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R94" s="1" t="inlineStr">
+      <c r="S94" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S94" s="1" t="inlineStr">
+      <c r="T94" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T94" s="1" t="inlineStr">
+      <c r="U94" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U94" s="1" t="inlineStr">
+      <c r="V94" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V94" s="1" t="inlineStr">
+      <c r="W94" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W94" s="1" t="inlineStr">
+      <c r="X94" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X94" s="1" t="inlineStr">
+      <c r="Y94" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y94" s="1" t="inlineStr">
+      <c r="Z94" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z94" s="1" t="inlineStr">
+      <c r="AA94" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA94" s="1" t="inlineStr">
+      <c r="AB94" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB94" s="1" t="inlineStr">
+      <c r="AC94" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC94" s="1" t="inlineStr">
+      <c r="AD94" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8422,77 +8543,77 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Sumo Tackle</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Sumo Tackle</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>e0cfa7e4-a40c-473d-855d-29a6ffe1d959</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t>3636b746-4ea7-42ff-8f55-04bfee8244df</t>
         </is>
@@ -8509,102 +8630,102 @@
           <t>b+1+2 ,2</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>– Fake Tackle Upper</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Sumo Tackle – Fake Tackle Upper</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>90,12</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="U96" t="inlineStr">
         <is>
           <t>!h</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>Fake Tackle Upper is blockable.</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>cb678e79-eafe-4a37-b7d2-bf5e6a95428f</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t>354d5860-71bd-4a66-99af-97d183cec5c4</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
+      <c r="AC96" t="inlineStr">
         <is>
           <t>e0cfa7e4-a40c-473d-855d-29a6ffe1d959</t>
         </is>
@@ -8621,72 +8742,72 @@
           <t>b+1+2,D</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>– Splits</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Sumo Tackle – Splits</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>90,-</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="U97" t="inlineStr">
         <is>
           <t>!-</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>2fd36c6a-c28a-4b9d-b8c6-0a15df9d7209</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>51570fdd-31bf-4bca-af01-61a257504a1e</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>e0cfa7e4-a40c-473d-855d-29a6ffe1d959</t>
         </is>
@@ -8723,125 +8844,130 @@
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F100" s="1" t="inlineStr">
+      <c r="G100" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr">
+      <c r="H100" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H100" s="1" t="inlineStr">
+      <c r="I100" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I100" s="1" t="inlineStr">
+      <c r="J100" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J100" s="1" t="inlineStr">
+      <c r="K100" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K100" s="1" t="inlineStr">
+      <c r="L100" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L100" s="1" t="inlineStr">
+      <c r="M100" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M100" s="1" t="inlineStr">
+      <c r="N100" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N100" s="1" t="inlineStr">
+      <c r="O100" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O100" s="1" t="inlineStr">
+      <c r="P100" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P100" s="1" t="inlineStr">
+      <c r="Q100" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q100" s="1" t="inlineStr">
+      <c r="R100" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R100" s="1" t="inlineStr">
+      <c r="S100" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S100" s="1" t="inlineStr">
+      <c r="T100" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T100" s="1" t="inlineStr">
+      <c r="U100" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U100" s="1" t="inlineStr">
+      <c r="V100" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V100" s="1" t="inlineStr">
+      <c r="W100" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W100" s="1" t="inlineStr">
+      <c r="X100" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X100" s="1" t="inlineStr">
+      <c r="Y100" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y100" s="1" t="inlineStr">
+      <c r="Z100" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z100" s="1" t="inlineStr">
+      <c r="AA100" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA100" s="1" t="inlineStr">
+      <c r="AB100" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB100" s="1" t="inlineStr">
+      <c r="AC100" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC100" s="1" t="inlineStr">
+      <c r="AD100" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
